--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/预案版本信息表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/预案版本信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-14T13:03:57.734087+00:00</t>
+          <t>2026-06-14T13:32:26.245439+00:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -1033,6 +1033,49 @@
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
+        <is>
+          <t>56A0TXN项目交付预案</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>56A0TXN</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>京东三期</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>何博</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-06-13T08:27:16.364558+00:00</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>何博</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-06-14T13:30:44.595368+00:00</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
         <is>
           <t>56A0TXN项目交付预案</t>
         </is>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/预案版本信息表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/预案版本信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-14T13:32:26.245439+00:00</t>
+          <t>2026-06-14T14:04:04.537171+00:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -1076,6 +1076,49 @@
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
+        <is>
+          <t>56A0TXN项目交付预案</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>56A0TXN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>京东三期</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>何博</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-06-13T08:27:16.364558+00:00</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>何博</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-06-14T14:03:57.707388+00:00</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
         <is>
           <t>56A0TXN项目交付预案</t>
         </is>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/预案版本信息表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/预案版本信息表.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-14T14:04:04.537171+00:00</t>
+          <t>2026-06-15T06:20:30.200469+00:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/预案版本信息表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/预案版本信息表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,22 +481,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>liwen</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-06-13T08:27:16.364558+00:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>何博</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-06-13T08:27:16.364558+00:00</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>何博</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-15T07:06:16.896772+00:00</t>
+          <t>2026-06-16T01:15:44.368351+00:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -524,7 +524,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>何博</t>
+          <t>liwen</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1119,6 +1119,49 @@
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
+        <is>
+          <t>56A0TXN项目交付预案</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>56A0TXN</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>京东三期</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>liwen</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-06-13T08:27:16.364558+00:00</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>liwen</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-06-15T09:17:39.490398+00:00</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
         <is>
           <t>56A0TXN项目交付预案</t>
         </is>
